--- a/docs/data/jp/xlsx/5574.xlsx
+++ b/docs/data/jp/xlsx/5574.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -759,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC150"/>
+  <dimension ref="A1:AC156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4205,11 +4208,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>2275</v>
+        <v>2346</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5446,7 +5449,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5695,1457 +5698,1662 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>233.833</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>250.226</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>207.791</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>230.107</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>281.897</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>405.161</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>320.26</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>341.79</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>493.737</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>499.065</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>353.561</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>439.065</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>235.264</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>230.107</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>341.79</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>439.065</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>419.536</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>521.077</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>412.937</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>490.744</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>486.826</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>634.066</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>564.932</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>550.477</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>704.83</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>653.546</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>664.266</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>769.689</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>439.399</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>490.744</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>550.477</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>769.689</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>362.782</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>375.582</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>423.703</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>391.885</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>392.215</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>438.701</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>455.325</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>504.173</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>485.567</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>488.203</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>482.044</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>625.888</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>415.449</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>391.885</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>504.173</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>625.888</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>56.754</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>145.494</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>-10.765</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>98.858</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>94.611</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>195.365</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>109.606</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>46.304</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>219.263</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>165.342</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>182.223</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>143.801</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>98.858</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>46.304</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>143.801</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>판매비와 관리비</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n">
+        <v>362.782</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>375.582</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0</v>
+        <v>423.703</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.283</v>
+        <v>391.885</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>392.215</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>438.701</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>0</v>
+        <v>455.325</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>3.919</v>
+        <v>504.173</v>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>485.567</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>488.203</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>0</v>
+        <v>482.044</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>6.258</v>
+        <v>625.888</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.013</v>
+        <v>415.449</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.283</v>
+        <v>391.885</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>3.919</v>
+        <v>504.173</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>6.258</v>
+        <v>625.888</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>56.754</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>145.494</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>-10.765</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>98.858</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>94.611</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>195.365</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>109.606</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>46.304</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>219.263</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>165.342</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>182.223</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>143.801</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>98.858</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>46.304</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>143.801</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>수수료 수익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>2.134</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>2.134</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>수탁연구 수입</t>
-        </is>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>0</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C87" s="22" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="D87" s="22" t="n">
-        <v>0.166</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="E87" s="22" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="G87" s="22" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="H87" s="22" t="n">
-        <v>0.743</v>
+        <v>0.283</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="K87" s="22" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="L87" s="22" t="n">
-        <v>0.519</v>
+        <v>3.919</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>1.634</v>
+        <v>6.258</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>-0.505</v>
+        <v>0.013</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>0.112</v>
+        <v>0.283</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>0.121</v>
+        <v>3.919</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>1.634</v>
+        <v>6.258</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="F88" s="22" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="G88" s="22" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>2.621</v>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>0.301</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="J88" s="22" t="n">
-        <v>4.312</v>
-      </c>
-      <c r="K88" s="22" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L88" s="22" t="n">
-        <v>5.623</v>
-      </c>
-      <c r="M88" s="22" t="n">
-        <v>10.357</v>
+        <v>0</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>34.573</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>4.312</v>
+        <v>0</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>34.573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>수수료 수익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>0.079</v>
+        <v>0.381</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>0.08</v>
+        <v>0.323</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>0.081</v>
+        <v>0.135</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>0.053</v>
+        <v>0.149</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>0</v>
+        <v>0.271</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>0.439</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>0</v>
+        <v>2.134</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>0.08</v>
+        <v>0.749</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>0.053</v>
+        <v>0.149</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>0</v>
+        <v>2.134</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="D90" s="22" t="n">
-        <v>0</v>
+          <t>수탁연구 수입</t>
+        </is>
       </c>
       <c r="E90" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="G90" s="22" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="I90" s="22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="M90" s="22" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>0.09</v>
+        <v>0</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="W90" s="22" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="X90" s="22" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>0.366</v>
+        <v>0.251</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>0.699</v>
+        <v>0.166</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>0.12</v>
+        <v>0.156</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0.324</v>
+        <v>0.112</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>0.155</v>
+        <v>0.104</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0.213</v>
+        <v>0.743</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>0.061</v>
+        <v>0.107</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>0.699</v>
+        <v>0.121</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>0.27</v>
+        <v>0.341</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0.3</v>
+        <v>0.519</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>0.062</v>
+        <v>0.459</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>0.234</v>
+        <v>1.634</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>19.94</v>
+        <v>-0.505</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>0.324</v>
+        <v>0.112</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>0.699</v>
+        <v>0.121</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>0.234</v>
+        <v>1.634</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>수탁연구 비용</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>0.507</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>2.621</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>4.312</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>5.623</v>
+      </c>
+      <c r="M92" s="22" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="N92" s="22" t="n">
+        <v>34.573</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="W92" s="22" t="n">
+        <v>4.312</v>
+      </c>
+      <c r="X92" s="22" t="n">
+        <v>34.573</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>3.682</v>
+        <v>0.081</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="G93" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="I93" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="K93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>-1.822</v>
+        <v>0.08</v>
       </c>
       <c r="V93" s="22" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="W93" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W93" s="22" t="n">
-        <v>-0.001</v>
-      </c>
       <c r="X93" s="22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0.469</v>
+        <v>0.023</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>3.883</v>
+        <v>0</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>0.514</v>
+        <v>0.135</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>0.623</v>
+        <v>0.467</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>0.45</v>
+        <v>0.123</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>0.051</v>
+        <v>-0.01</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>0.747</v>
+        <v>0.048</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>0.539</v>
+        <v>0.269</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>0.629</v>
+        <v>0.097</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>0.081</v>
+        <v>0.018</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="U94" s="22" t="n">
-        <v>20.282</v>
+        <v>0.09</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0.514</v>
+        <v>0.135</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>0.747</v>
+        <v>0.048</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>0.623</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>56.916</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>145.224</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>-14.359</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>98.89100000000001</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>94.717</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>197.536</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>109.857</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>49.868</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>219.264</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>170.336</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>192.499</v>
-      </c>
-      <c r="N95" s="12" t="n">
-        <v>177.751</v>
-      </c>
-      <c r="U95" s="12" t="n">
-        <v>3.925</v>
-      </c>
-      <c r="V95" s="12" t="n">
-        <v>98.89100000000001</v>
-      </c>
-      <c r="W95" s="12" t="n">
-        <v>49.868</v>
-      </c>
-      <c r="X95" s="12" t="n">
-        <v>177.751</v>
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>주식교부비</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="U95" s="22" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="X95" s="22" t="n">
+        <v>0.234</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>56.916</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>145.224</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>-14.359</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>98.89100000000001</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>94.717</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>197.536</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>109.857</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>49.868</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>219.264</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>170.336</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>192.499</v>
-      </c>
-      <c r="N96" s="12" t="n">
-        <v>177.751</v>
-      </c>
-      <c r="U96" s="12" t="n">
-        <v>3.925</v>
-      </c>
-      <c r="V96" s="12" t="n">
-        <v>98.89100000000001</v>
-      </c>
-      <c r="W96" s="12" t="n">
-        <v>49.868</v>
-      </c>
-      <c r="X96" s="12" t="n">
-        <v>177.751</v>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>수탁연구 비용</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>3.682</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>0.3</v>
       </c>
       <c r="U97" s="22" t="n">
-        <v>86.935</v>
+        <v>-1.822</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>9.222</v>
+        <v>0.469</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>22.523</v>
+        <v>0.779</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>2.855</v>
+        <v>3.883</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>33.359</v>
+        <v>0.514</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>9.356999999999999</v>
+        <v>0.623</v>
       </c>
       <c r="H98" s="22" t="n">
-        <v>38.602</v>
+        <v>0.45</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="J98" s="22" t="n">
-        <v>-44.816</v>
+        <v>0.747</v>
       </c>
       <c r="K98" s="22" t="n">
-        <v>37.186</v>
+        <v>0.539</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>16.18</v>
+        <v>0.629</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-184.773</v>
+        <v>0.081</v>
       </c>
       <c r="N98" s="22" t="n">
-        <v>-174.648</v>
+        <v>0.623</v>
       </c>
       <c r="U98" s="22" t="n">
-        <v>-43.559</v>
+        <v>20.282</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>33.359</v>
+        <v>0.514</v>
       </c>
       <c r="W98" s="22" t="n">
-        <v>-44.816</v>
+        <v>0.747</v>
       </c>
       <c r="X98" s="22" t="n">
-        <v>-174.648</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>56.916</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>145.224</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>-14.359</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>98.89100000000001</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>94.717</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>197.536</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>109.857</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>49.868</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>219.264</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>170.336</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>192.499</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>177.751</v>
+      </c>
+      <c r="U99" s="12" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>98.89100000000001</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>49.868</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>177.751</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="17">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="17">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="17">
+        <f>IF(OR(L99="",H99=""),"",IF(H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M100" s="17">
+        <f>IF(OR(M99="",I99=""),"",IF(I99&lt;=0,"",IFERROR(M99/I99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="17">
+        <f>IF(OR(N99="",J99=""),"",IF(J99&lt;=0,"",IFERROR(N99/J99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U100" s="17">
+        <f>IF(OR(U99="",T99=""),"",IF(T99&lt;=0,"",IFERROR(U99/T99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="17">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="17">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X100" s="17">
+        <f>IF(OR(X99="",W99=""),"",IF(W99&lt;=0,"",IFERROR(X99/W99-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>56.916</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>145.224</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>-14.359</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>98.89100000000001</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>94.717</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>197.536</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>109.857</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>49.868</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>219.264</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>170.336</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>192.499</v>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>177.751</v>
+      </c>
+      <c r="U101" s="12" t="n">
+        <v>3.925</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>98.89100000000001</v>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>49.868</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>177.751</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="U102" s="22" t="n">
+        <v>86.935</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>9.222</v>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>22.523</v>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>33.359</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>9.356999999999999</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>38.602</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>-44.816</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>37.186</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>-184.773</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>-174.648</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>-43.559</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>33.359</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>-44.816</v>
+      </c>
+      <c r="X103" s="22" t="n">
+        <v>-174.648</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C104" s="12" t="n">
         <v>47.693</v>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D104" s="12" t="n">
         <v>122.701</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E104" s="12" t="n">
         <v>-17.214</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F104" s="12" t="n">
         <v>65.532</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G104" s="12" t="n">
         <v>85.35899999999999</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H104" s="12" t="n">
         <v>158.935</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I104" s="12" t="n">
         <v>109.289</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J104" s="12" t="n">
         <v>94.685</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K104" s="12" t="n">
         <v>182.078</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="L104" s="12" t="n">
         <v>154.155</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="M104" s="12" t="n">
         <v>377.274</v>
       </c>
-      <c r="N99" s="12" t="n">
+      <c r="N104" s="12" t="n">
         <v>352.398</v>
       </c>
-      <c r="U99" s="12" t="n">
+      <c r="U104" s="12" t="n">
         <v>47.485</v>
       </c>
-      <c r="V99" s="12" t="n">
+      <c r="V104" s="12" t="n">
         <v>65.532</v>
       </c>
-      <c r="W99" s="12" t="n">
+      <c r="W104" s="12" t="n">
         <v>94.685</v>
       </c>
-      <c r="X99" s="12" t="n">
+      <c r="X104" s="12" t="n">
         <v>352.398</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G105" s="17">
+        <f>IF(OR(G104="",C104=""),"",IF(C104&lt;=0,"",IFERROR(G104/C104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(OR(H104="",D104=""),"",IF(D104&lt;=0,"",IFERROR(H104/D104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I105" s="17">
+        <f>IF(OR(I104="",E104=""),"",IF(E104&lt;=0,"",IFERROR(I104/E104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>IF(OR(J104="",F104=""),"",IF(F104&lt;=0,"",IFERROR(J104/F104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF(OR(K104="",G104=""),"",IF(G104&lt;=0,"",IFERROR(K104/G104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L105" s="17">
+        <f>IF(OR(L104="",H104=""),"",IF(H104&lt;=0,"",IFERROR(L104/H104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M105" s="17">
+        <f>IF(OR(M104="",I104=""),"",IF(I104&lt;=0,"",IFERROR(M104/I104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="17">
+        <f>IF(OR(N104="",J104=""),"",IF(J104&lt;=0,"",IFERROR(N104/J104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U105" s="17">
+        <f>IF(OR(U104="",T104=""),"",IF(T104&lt;=0,"",IFERROR(U104/T104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V105" s="17">
+        <f>IF(OR(V104="",U104=""),"",IF(U104&lt;=0,"",IFERROR(V104/U104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W105" s="17">
+        <f>IF(OR(W104="",V104=""),"",IF(V104&lt;=0,"",IFERROR(W104/V104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X105" s="17">
+        <f>IF(OR(X104="",W104=""),"",IF(W104&lt;=0,"",IFERROR(X104/W104-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B101" s="44" t="inlineStr">
+      <c r="B107" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-      <c r="J101" s="18" t="n"/>
-      <c r="K101" s="18" t="n"/>
-      <c r="L101" s="18" t="n"/>
-      <c r="M101" s="18" t="n"/>
-      <c r="N101" s="18" t="n"/>
-      <c r="O101" s="18" t="n"/>
-      <c r="P101" s="18" t="n"/>
-      <c r="Q101" s="18" t="n"/>
-      <c r="R101" s="18" t="n"/>
-      <c r="S101" s="18" t="n"/>
-      <c r="T101" s="18" t="n"/>
-      <c r="U101" s="18" t="n"/>
-      <c r="V101" s="18" t="n"/>
-      <c r="W101" s="18" t="n"/>
-      <c r="X101" s="18" t="n"/>
-      <c r="Y101" s="18" t="n"/>
-      <c r="Z101" s="18" t="n"/>
-      <c r="AA101" s="18" t="n"/>
-      <c r="AB101" s="18" t="n"/>
-      <c r="AC101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+      <c r="J107" s="18" t="n"/>
+      <c r="K107" s="18" t="n"/>
+      <c r="L107" s="18" t="n"/>
+      <c r="M107" s="18" t="n"/>
+      <c r="N107" s="18" t="n"/>
+      <c r="O107" s="18" t="n"/>
+      <c r="P107" s="18" t="n"/>
+      <c r="Q107" s="18" t="n"/>
+      <c r="R107" s="18" t="n"/>
+      <c r="S107" s="18" t="n"/>
+      <c r="T107" s="18" t="n"/>
+      <c r="U107" s="18" t="n"/>
+      <c r="V107" s="18" t="n"/>
+      <c r="W107" s="18" t="n"/>
+      <c r="X107" s="18" t="n"/>
+      <c r="Y107" s="18" t="n"/>
+      <c r="Z107" s="18" t="n"/>
+      <c r="AA107" s="18" t="n"/>
+      <c r="AB107" s="18" t="n"/>
+      <c r="AC107" s="18" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="J102" s="5" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr">
+      <c r="K108" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L108" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="M102" s="5" t="inlineStr">
+      <c r="M108" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="N102" s="5" t="inlineStr">
+      <c r="N108" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="O102" s="5" t="inlineStr">
+      <c r="O108" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P102" s="5" t="inlineStr">
+      <c r="P108" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q102" s="5" t="inlineStr">
+      <c r="Q108" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R102" s="5" t="inlineStr">
+      <c r="R108" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S102" s="5" t="inlineStr">
+      <c r="S108" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T102" s="5" t="inlineStr">
+      <c r="T108" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U102" s="5" t="inlineStr">
+      <c r="U108" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V102" s="5" t="inlineStr">
+      <c r="V108" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W102" s="5" t="inlineStr">
+      <c r="W108" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X102" s="5" t="inlineStr">
+      <c r="X108" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y102" s="5" t="inlineStr">
+      <c r="Y108" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z102" s="5" t="inlineStr">
+      <c r="Z108" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA102" s="5" t="inlineStr">
+      <c r="AA108" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB102" s="5" t="inlineStr">
+      <c r="AB108" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC102" s="5" t="inlineStr">
+      <c r="AC108" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="D103" s="12" t="n">
+      <c r="D109" s="12" t="n">
         <v>202.14</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="F109" s="12" t="n">
         <v>286.672</v>
       </c>
-      <c r="H103" s="12" t="n">
+      <c r="H109" s="12" t="n">
         <v>292.253</v>
       </c>
-      <c r="J103" s="12" t="n">
+      <c r="J109" s="12" t="n">
         <v>451.978</v>
       </c>
-      <c r="L103" s="12" t="n">
+      <c r="L109" s="12" t="n">
         <v>389.6</v>
       </c>
-      <c r="N103" s="12" t="n">
+      <c r="N109" s="12" t="n">
         <v>759.85</v>
       </c>
-      <c r="T103" s="12" t="n">
+      <c r="T109" s="12" t="n">
         <v>-194.072</v>
       </c>
-      <c r="U103" s="12" t="n">
+      <c r="U109" s="12" t="n">
         <v>379.757</v>
       </c>
-      <c r="V103" s="12" t="n">
+      <c r="V109" s="12" t="n">
         <v>286.672</v>
       </c>
-      <c r="W103" s="12" t="n">
+      <c r="W109" s="12" t="n">
         <v>451.978</v>
       </c>
-      <c r="X103" s="12" t="n">
+      <c r="X109" s="12" t="n">
         <v>759.85</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>1.512</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>5.805</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>5.334</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>12.888</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>7.212</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="T104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>5.805</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>12.888</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>16.76</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>신주예약권 환입이익</t>
-        </is>
-      </c>
-      <c r="T105" s="22" t="n">
-        <v>-1.746</v>
-      </c>
-      <c r="U105" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="22" t="n">
-        <v>-0.505</v>
-      </c>
-      <c r="U106" s="22" t="n">
-        <v>-0.265</v>
-      </c>
-      <c r="V106" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="H107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>2.851</v>
-      </c>
-      <c r="W107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="22" t="n">
-        <v>2.851</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="D108" s="22" t="n">
-        <v>-10.794</v>
-      </c>
-      <c r="F108" s="22" t="n">
-        <v>-7.286</v>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>51.039</v>
-      </c>
-      <c r="J108" s="22" t="n">
-        <v>40.808</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>-0.447</v>
-      </c>
-      <c r="N108" s="22" t="n">
-        <v>26.032</v>
-      </c>
-      <c r="T108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>124.139</v>
-      </c>
-      <c r="V108" s="22" t="n">
-        <v>-7.286</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>40.808</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>26.032</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>수주손실 충당금 증감</t>
-        </is>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>-4.467</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>임원 상여충당금 증감</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="D110" s="22" t="n">
+        <v>1.512</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>5.805</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>5.334</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>12.888</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>7.212</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="T110" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="22" t="n">
-        <v>20.256</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>51.479</v>
-      </c>
-      <c r="L110" s="22" t="n">
-        <v>-38.612</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>-20.011</v>
+      <c r="U110" s="22" t="n">
+        <v>0.106</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>0</v>
+        <v>5.805</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>51.479</v>
+        <v>12.888</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>-20.011</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>-1.439</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>-5.358</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>-4.665</v>
+          <t>신주예약권 환입이익</t>
+        </is>
       </c>
       <c r="T111" s="22" t="n">
-        <v>-0.021</v>
+        <v>-1.746</v>
       </c>
       <c r="U111" s="22" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-5.358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>-5.358</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>-20.161</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-5.358</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>-20.161</v>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" s="22" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="D113" s="22" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>0.293</v>
+          <t>주식보상비용</t>
+        </is>
       </c>
       <c r="H113" s="22" t="n">
         <v>0</v>
@@ -7154,722 +7362,710 @@
         <v>0</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>0.232</v>
+        <v>0.95</v>
       </c>
       <c r="N113" s="22" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>0.293</v>
+        <v>2.851</v>
       </c>
       <c r="W113" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="22" t="n">
-        <v>0.232</v>
+        <v>2.851</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>-10.794</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>-7.286</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>51.039</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>40.808</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>-0.447</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>26.032</v>
       </c>
       <c r="T114" s="22" t="n">
-        <v>14.061</v>
+        <v>0</v>
       </c>
       <c r="U114" s="22" t="n">
-        <v>0</v>
+        <v>124.139</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>-7.286</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>40.808</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>26.032</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
-        </is>
-      </c>
-      <c r="D115" s="22" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>1.509</v>
-      </c>
-      <c r="H115" s="22" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>1.128</v>
-      </c>
-      <c r="L115" s="22" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>0.866</v>
+          <t>수주손실 충당금 증감</t>
+        </is>
       </c>
       <c r="T115" s="22" t="n">
+        <v>-4.467</v>
+      </c>
+      <c r="U115" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>1.509</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>1.128</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>0.866</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="D116" s="22" t="n">
-        <v>-149.864</v>
+        <v>0</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>-95.554</v>
+        <v>0</v>
       </c>
       <c r="H116" s="22" t="n">
-        <v>-348.724</v>
+        <v>20.256</v>
       </c>
       <c r="J116" s="22" t="n">
-        <v>-10.234</v>
+        <v>51.479</v>
       </c>
       <c r="L116" s="22" t="n">
-        <v>-104.703</v>
+        <v>-38.612</v>
       </c>
       <c r="N116" s="22" t="n">
-        <v>-384.138</v>
-      </c>
-      <c r="T116" s="22" t="n">
-        <v>36.205</v>
-      </c>
-      <c r="U116" s="22" t="n">
-        <v>-206.27</v>
+        <v>-20.011</v>
       </c>
       <c r="V116" s="22" t="n">
-        <v>-95.554</v>
+        <v>0</v>
       </c>
       <c r="W116" s="22" t="n">
-        <v>-10.234</v>
+        <v>51.479</v>
       </c>
       <c r="X116" s="22" t="n">
-        <v>-384.138</v>
+        <v>-20.011</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>재공품 증감</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
-        <v>-1.881</v>
+        <v>-0.017</v>
+      </c>
+      <c r="F117" s="22" t="n">
+        <v>-0.3</v>
       </c>
       <c r="H117" s="22" t="n">
-        <v>-7.616</v>
+        <v>-1.439</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>-5.358</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>0.819</v>
+        <v>-4.665</v>
+      </c>
+      <c r="T117" s="22" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="U117" s="22" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="V117" s="22" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="W117" s="22" t="n">
+        <v>-5.358</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="F118" s="22" t="n">
-        <v>0.301</v>
+          <t>이자·배당금 수익</t>
+        </is>
       </c>
       <c r="J118" s="22" t="n">
-        <v>-7.542</v>
+        <v>-5.358</v>
       </c>
       <c r="N118" s="22" t="n">
-        <v>1.926</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>-42.04</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>64.617</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>0.301</v>
+        <v>-20.161</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>-7.542</v>
+        <v>-5.358</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>1.926</v>
+        <v>-20.161</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>저장품 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
-        <v>2.505</v>
+        <v>0.159</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>0.187</v>
+        <v>0.293</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>-0.819</v>
+        <v>0</v>
       </c>
       <c r="J119" s="22" t="n">
-        <v>2.184</v>
+        <v>0</v>
       </c>
       <c r="L119" s="22" t="n">
-        <v>0.824</v>
+        <v>0.232</v>
       </c>
       <c r="N119" s="22" t="n">
-        <v>1.834</v>
+        <v>0.232</v>
       </c>
       <c r="T119" s="22" t="n">
-        <v>5.886</v>
+        <v>0.32</v>
       </c>
       <c r="U119" s="22" t="n">
-        <v>-4.176</v>
+        <v>0.319</v>
       </c>
       <c r="V119" s="22" t="n">
-        <v>0.187</v>
+        <v>0.293</v>
       </c>
       <c r="W119" s="22" t="n">
-        <v>2.184</v>
+        <v>0</v>
       </c>
       <c r="X119" s="22" t="n">
-        <v>1.834</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>미수금 증감</t>
-        </is>
-      </c>
-      <c r="D120" s="22" t="n">
-        <v>-182.303</v>
-      </c>
-      <c r="F120" s="22" t="n">
-        <v>-684.736</v>
-      </c>
-      <c r="H120" s="22" t="n">
-        <v>631.751</v>
-      </c>
-      <c r="J120" s="22" t="n">
-        <v>684.1180000000001</v>
-      </c>
-      <c r="L120" s="22" t="n">
-        <v>-79.133</v>
-      </c>
-      <c r="N120" s="22" t="n">
-        <v>-8.744999999999999</v>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="T120" s="22" t="n">
+        <v>14.061</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>11.115</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>-684.736</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>684.1180000000001</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>-8.744999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>주식교부비</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
-        <v>0.531</v>
+        <v>1.065</v>
       </c>
       <c r="F121" s="22" t="n">
-        <v>0.016</v>
+        <v>1.509</v>
       </c>
       <c r="H121" s="22" t="n">
-        <v>0.019</v>
+        <v>0.368</v>
       </c>
       <c r="J121" s="22" t="n">
-        <v>0.482</v>
+        <v>1.128</v>
       </c>
       <c r="L121" s="22" t="n">
-        <v>-0.003</v>
+        <v>0.57</v>
       </c>
       <c r="N121" s="22" t="n">
-        <v>0.218</v>
+        <v>0.866</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>-2.773</v>
+        <v>0</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>-0.322</v>
+        <v>24.47</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>0.016</v>
+        <v>1.509</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>0.482</v>
+        <v>1.128</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>0.218</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="D122" s="22" t="n">
-        <v>180.733</v>
+        <v>-149.864</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>-26.409</v>
+        <v>-95.554</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>56.723</v>
+        <v>-348.724</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>71.988</v>
+        <v>-10.234</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>59.347</v>
+        <v>-104.703</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>136.928</v>
+        <v>-384.138</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>-19.853</v>
+        <v>36.205</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>-64.20999999999999</v>
+        <v>-206.27</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>-26.409</v>
+        <v>-95.554</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>71.988</v>
+        <v>-10.234</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>136.928</v>
+        <v>-384.138</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
-      </c>
-      <c r="F123" s="22" t="n">
-        <v>14.725</v>
+          <t>재공품 증감</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>-1.881</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>-21.368</v>
-      </c>
-      <c r="J123" s="22" t="n">
-        <v>132.447</v>
+        <v>-7.616</v>
       </c>
       <c r="L123" s="22" t="n">
-        <v>-132.254</v>
-      </c>
-      <c r="N123" s="22" t="n">
-        <v>-148.116</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>14.725</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>132.447</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>-148.116</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>미지급법인세(외형표준과세) 증감</t>
-        </is>
-      </c>
-      <c r="D124" s="22" t="n">
-        <v>-15.18</v>
+          <t>재고자산 증감</t>
+        </is>
       </c>
       <c r="F124" s="22" t="n">
-        <v>-18.911</v>
-      </c>
-      <c r="H124" s="22" t="n">
-        <v>4.784</v>
+        <v>0.301</v>
       </c>
       <c r="J124" s="22" t="n">
-        <v>7.066</v>
-      </c>
-      <c r="L124" s="22" t="n">
-        <v>1.414</v>
+        <v>-7.542</v>
       </c>
       <c r="N124" s="22" t="n">
-        <v>6.63</v>
+        <v>1.926</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>-7.093</v>
+        <v>-42.04</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>32.013</v>
+        <v>64.617</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>-18.911</v>
+        <v>0.301</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>7.066</v>
+        <v>-7.542</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>6.63</v>
+        <v>1.926</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>저장품 증감</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
-        <v>-110.488</v>
+        <v>2.505</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>-103.357</v>
+        <v>0.187</v>
       </c>
       <c r="H125" s="22" t="n">
-        <v>72.06100000000001</v>
+        <v>-0.819</v>
       </c>
       <c r="J125" s="22" t="n">
-        <v>187.661</v>
+        <v>2.184</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>-103.239</v>
+        <v>0.824</v>
       </c>
       <c r="N125" s="22" t="n">
-        <v>-138.76</v>
+        <v>1.834</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>-38.2</v>
+        <v>5.886</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>101.853</v>
+        <v>-4.176</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>-103.357</v>
+        <v>0.187</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>187.661</v>
+        <v>2.184</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>-138.76</v>
+        <v>1.834</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>미수금 증감</t>
         </is>
       </c>
       <c r="D126" s="22" t="n">
-        <v>-81.88200000000001</v>
+        <v>-182.303</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>-627.043</v>
+        <v>-684.736</v>
       </c>
       <c r="H126" s="22" t="n">
-        <v>754.624</v>
+        <v>631.751</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>1621.096</v>
+        <v>684.1180000000001</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>-2.088</v>
+        <v>-79.133</v>
       </c>
       <c r="N126" s="22" t="n">
-        <v>234.196</v>
-      </c>
-      <c r="T126" s="22" t="n">
-        <v>-254.299</v>
+        <v>-8.744999999999999</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>463.123</v>
+        <v>11.115</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>-627.043</v>
+        <v>-684.736</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>1621.096</v>
+        <v>684.1180000000001</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>234.196</v>
+        <v>-8.744999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>이자 수취</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
-        <v>0.017</v>
+        <v>0.531</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>0.3</v>
+        <v>0.016</v>
       </c>
       <c r="H127" s="22" t="n">
-        <v>1.439</v>
+        <v>0.019</v>
       </c>
       <c r="J127" s="22" t="n">
-        <v>5.358</v>
+        <v>0.482</v>
       </c>
       <c r="L127" s="22" t="n">
-        <v>4.665</v>
+        <v>-0.003</v>
+      </c>
+      <c r="N127" s="22" t="n">
+        <v>0.218</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>0.021</v>
+        <v>-2.773</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>0.022</v>
+        <v>-0.322</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>0.3</v>
+        <v>0.016</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>5.358</v>
+        <v>0.482</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>0.218</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
+          <t>미지급금 증감</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>180.733</v>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>-26.409</v>
+      </c>
+      <c r="H128" s="22" t="n">
+        <v>56.723</v>
       </c>
       <c r="J128" s="22" t="n">
-        <v>5.358</v>
+        <v>71.988</v>
+      </c>
+      <c r="L128" s="22" t="n">
+        <v>59.347</v>
       </c>
       <c r="N128" s="22" t="n">
-        <v>20.161</v>
+        <v>136.928</v>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>-19.853</v>
+      </c>
+      <c r="U128" s="22" t="n">
+        <v>-64.20999999999999</v>
+      </c>
+      <c r="V128" s="22" t="n">
+        <v>-26.409</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>5.358</v>
+        <v>71.988</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>20.161</v>
+        <v>136.928</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="D129" s="22" t="n">
-        <v>-0.159</v>
+          <t>계약부채 증감</t>
+        </is>
       </c>
       <c r="F129" s="22" t="n">
-        <v>-0.293</v>
+        <v>14.725</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>0</v>
+        <v>-21.368</v>
       </c>
       <c r="J129" s="22" t="n">
-        <v>0</v>
+        <v>132.447</v>
       </c>
       <c r="L129" s="22" t="n">
-        <v>-0.232</v>
+        <v>-132.254</v>
       </c>
       <c r="N129" s="22" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>-0.319</v>
+        <v>-148.116</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>-0.293</v>
+        <v>14.725</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>0</v>
+        <v>132.447</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>-0.232</v>
+        <v>-148.116</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>미지급법인세(외형표준과세) 증감</t>
         </is>
       </c>
       <c r="D130" s="22" t="n">
-        <v>-88.649</v>
+        <v>-15.18</v>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>-18.911</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>11.299</v>
+        <v>4.784</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>7.066</v>
       </c>
       <c r="L130" s="22" t="n">
-        <v>-53.65</v>
+        <v>1.414</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="T130" s="22" t="n">
+        <v>-7.093</v>
+      </c>
+      <c r="U130" s="22" t="n">
+        <v>32.013</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>-18.911</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>7.066</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>6.63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>-88.649</v>
+        <v>-110.488</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>-132.974</v>
+        <v>-103.357</v>
+      </c>
+      <c r="H131" s="22" t="n">
+        <v>72.06100000000001</v>
       </c>
       <c r="J131" s="22" t="n">
-        <v>-5.213</v>
+        <v>187.661</v>
+      </c>
+      <c r="L131" s="22" t="n">
+        <v>-103.239</v>
       </c>
       <c r="N131" s="22" t="n">
-        <v>-88.92</v>
+        <v>-138.76</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>-2.288</v>
+        <v>-38.2</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-2.293</v>
+        <v>101.853</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>-132.974</v>
+        <v>-103.357</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-5.213</v>
+        <v>187.661</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-88.92</v>
+        <v>-138.76</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>-81.88200000000001</v>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>-627.043</v>
+      </c>
+      <c r="H132" s="22" t="n">
+        <v>754.624</v>
+      </c>
+      <c r="J132" s="22" t="n">
+        <v>1621.096</v>
+      </c>
+      <c r="L132" s="22" t="n">
+        <v>-2.088</v>
+      </c>
+      <c r="N132" s="22" t="n">
+        <v>234.196</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>3.392</v>
+        <v>-254.299</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>0</v>
+        <v>463.123</v>
+      </c>
+      <c r="V132" s="22" t="n">
+        <v>-627.043</v>
+      </c>
+      <c r="W132" s="22" t="n">
+        <v>1621.096</v>
+      </c>
+      <c r="X132" s="22" t="n">
+        <v>234.196</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="n">
-        <v>-170.674</v>
-      </c>
-      <c r="F133" s="12" t="n">
-        <v>-760.011</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>767.362</v>
-      </c>
-      <c r="J133" s="12" t="n">
-        <v>1621.241</v>
-      </c>
-      <c r="L133" s="12" t="n">
-        <v>-51.306</v>
-      </c>
-      <c r="N133" s="12" t="n">
-        <v>165.206</v>
-      </c>
-      <c r="T133" s="12" t="n">
-        <v>-253.494</v>
-      </c>
-      <c r="U133" s="12" t="n">
-        <v>460.532</v>
-      </c>
-      <c r="V133" s="12" t="n">
-        <v>-760.011</v>
-      </c>
-      <c r="W133" s="12" t="n">
-        <v>1621.241</v>
-      </c>
-      <c r="X133" s="12" t="n">
-        <v>165.206</v>
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>이자 수취</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H133" s="22" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="L133" s="22" t="n">
+        <v>4.665</v>
+      </c>
+      <c r="T133" s="22" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>5.358</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="D134" s="22" t="n">
-        <v>-7.123</v>
-      </c>
-      <c r="F134" s="22" t="n">
-        <v>-13.647</v>
-      </c>
-      <c r="H134" s="22" t="n">
-        <v>-9.09</v>
+          <t>이자·배당금 수취</t>
+        </is>
       </c>
       <c r="J134" s="22" t="n">
-        <v>-15.928</v>
-      </c>
-      <c r="L134" s="22" t="n">
-        <v>-8.179</v>
+        <v>5.358</v>
       </c>
       <c r="N134" s="22" t="n">
-        <v>-14.173</v>
-      </c>
-      <c r="T134" s="22" t="n">
-        <v>-14.061</v>
-      </c>
-      <c r="U134" s="22" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="V134" s="22" t="n">
-        <v>-13.647</v>
+        <v>20.161</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>-15.928</v>
+        <v>5.358</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>-14.173</v>
+        <v>20.161</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>-9.977</v>
+        <v>-0.159</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>-19.947</v>
+        <v>-0.293</v>
       </c>
       <c r="H135" s="22" t="n">
         <v>0</v>
@@ -7877,274 +8073,307 @@
       <c r="J135" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="L135" s="22" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="T135" s="22" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="U135" s="22" t="n">
-        <v>0</v>
+        <v>-0.319</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>-19.947</v>
+        <v>-0.293</v>
       </c>
       <c r="W135" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="X135" s="22" t="n">
+        <v>-0.232</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>종업원 대여금 회수</t>
+          <t>법인세 납부·환급</t>
         </is>
       </c>
       <c r="D136" s="22" t="n">
-        <v>4.998</v>
-      </c>
-      <c r="F136" s="22" t="n">
-        <v>4.998</v>
+        <v>-88.649</v>
       </c>
       <c r="H136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>4.998</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>0</v>
+        <v>11.299</v>
+      </c>
+      <c r="L136" s="22" t="n">
+        <v>-53.65</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>종업원 대여</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>-88.649</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>0</v>
+        <v>-132.974</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-5.213</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>-88.92</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>0</v>
+        <v>-2.288</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-4.998</v>
+        <v>-2.293</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>0</v>
+        <v>-132.974</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-5.213</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-88.92</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="H138" s="22" t="n">
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="T138" s="22" t="n">
+        <v>3.392</v>
+      </c>
+      <c r="U138" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="22" t="n">
-        <v>-324.351</v>
-      </c>
-      <c r="N138" s="22" t="n">
-        <v>-324.351</v>
-      </c>
-      <c r="W138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" s="22" t="n">
-        <v>-324.351</v>
-      </c>
     </row>
     <row r="139">
-      <c r="A139" s="20" t="inlineStr">
-        <is>
-          <t>보증금 납입</t>
-        </is>
-      </c>
-      <c r="F139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="22" t="n">
-        <v>-12.484</v>
-      </c>
-      <c r="N139" s="22" t="n">
-        <v>-13.123</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" s="22" t="n">
-        <v>-12.484</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>-13.123</v>
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>-170.674</v>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>-760.011</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>767.362</v>
+      </c>
+      <c r="J139" s="12" t="n">
+        <v>1621.241</v>
+      </c>
+      <c r="L139" s="12" t="n">
+        <v>-51.306</v>
+      </c>
+      <c r="N139" s="12" t="n">
+        <v>165.206</v>
+      </c>
+      <c r="T139" s="12" t="n">
+        <v>-253.494</v>
+      </c>
+      <c r="U139" s="12" t="n">
+        <v>460.532</v>
+      </c>
+      <c r="V139" s="12" t="n">
+        <v>-760.011</v>
+      </c>
+      <c r="W139" s="12" t="n">
+        <v>1621.241</v>
+      </c>
+      <c r="X139" s="12" t="n">
+        <v>165.206</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="D140" s="22" t="n">
-        <v>0.027</v>
+        <v>-7.123</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>0.027</v>
+        <v>-13.647</v>
       </c>
       <c r="H140" s="22" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="J140" s="22" t="n">
+        <v>-15.928</v>
+      </c>
+      <c r="L140" s="22" t="n">
+        <v>-8.179</v>
+      </c>
+      <c r="N140" s="22" t="n">
+        <v>-14.173</v>
+      </c>
+      <c r="T140" s="22" t="n">
+        <v>-14.061</v>
+      </c>
+      <c r="U140" s="22" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="V140" s="22" t="n">
+        <v>-13.647</v>
+      </c>
+      <c r="W140" s="22" t="n">
+        <v>-15.928</v>
+      </c>
+      <c r="X140" s="22" t="n">
+        <v>-14.173</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>-9.977</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>-19.947</v>
+      </c>
+      <c r="H141" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="22" t="n">
+      <c r="J141" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="22" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="N140" s="22" t="n">
-        <v>-52</v>
-      </c>
-      <c r="U140" s="22" t="n">
+      <c r="U141" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="22" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="W140" s="22" t="n">
+      <c r="V141" s="22" t="n">
+        <v>-19.947</v>
+      </c>
+      <c r="W141" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>-52</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D141" s="12" t="n">
-        <v>-12.075</v>
-      </c>
-      <c r="F141" s="12" t="n">
-        <v>-28.569</v>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>-9.09</v>
-      </c>
-      <c r="J141" s="12" t="n">
-        <v>-28.412</v>
-      </c>
-      <c r="L141" s="12" t="n">
-        <v>-332.686</v>
-      </c>
-      <c r="N141" s="12" t="n">
-        <v>-403.648</v>
-      </c>
-      <c r="T141" s="12" t="n">
-        <v>-14.061</v>
-      </c>
-      <c r="U141" s="12" t="n">
-        <v>-5.638</v>
-      </c>
-      <c r="V141" s="12" t="n">
-        <v>-28.569</v>
-      </c>
-      <c r="W141" s="12" t="n">
-        <v>-28.412</v>
-      </c>
-      <c r="X141" s="12" t="n">
-        <v>-403.648</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
-        </is>
-      </c>
-      <c r="T142" s="22" t="n">
-        <v>3.958</v>
+          <t>종업원 대여금 회수</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="n">
+        <v>4.998</v>
+      </c>
+      <c r="F142" s="22" t="n">
+        <v>4.998</v>
+      </c>
+      <c r="H142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U142" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="V142" s="22" t="n">
+        <v>4.998</v>
+      </c>
+      <c r="W142" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>종업원 대여</t>
         </is>
       </c>
       <c r="F143" s="22" t="n">
-        <v>-80</v>
-      </c>
-      <c r="J143" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="T143" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="U143" s="22" t="n">
-        <v>0</v>
+        <v>-4.998</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>-80</v>
-      </c>
-      <c r="W143" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="F144" s="22" t="n">
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="H144" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="22" t="n">
+      <c r="J144" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U144" s="22" t="n">
-        <v>1241.104</v>
-      </c>
-      <c r="V144" s="22" t="n">
+      <c r="L144" s="22" t="n">
+        <v>-324.351</v>
+      </c>
+      <c r="N144" s="22" t="n">
+        <v>-324.351</v>
+      </c>
+      <c r="W144" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="X144" s="22" t="n">
+        <v>-324.351</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
-      </c>
-      <c r="H145" s="22" t="n">
+          <t>보증금 납입</t>
+        </is>
+      </c>
+      <c r="F145" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J145" s="22" t="n">
+        <v>-12.484</v>
+      </c>
+      <c r="N145" s="22" t="n">
+        <v>-13.123</v>
+      </c>
+      <c r="V145" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L145" s="22" t="n">
-        <v>150</v>
-      </c>
-      <c r="N145" s="22" t="n">
-        <v>150</v>
-      </c>
       <c r="W145" s="22" t="n">
-        <v>0</v>
+        <v>-12.484</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>150</v>
+        <v>-13.123</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F146" s="22" t="n">
+        <v>0.027</v>
       </c>
       <c r="H146" s="22" t="n">
         <v>0</v>
@@ -8153,166 +8382,316 @@
         <v>0</v>
       </c>
       <c r="L146" s="22" t="n">
-        <v>-150</v>
+        <v>-0.155</v>
       </c>
       <c r="N146" s="22" t="n">
-        <v>-150</v>
+        <v>-52</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>0.027</v>
       </c>
       <c r="W146" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-150</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="20" t="inlineStr">
-        <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="D147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="22" t="n">
-        <v>-0.149</v>
-      </c>
-      <c r="J147" s="22" t="n">
-        <v>-0.272</v>
-      </c>
-      <c r="L147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="22" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="V147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" s="22" t="n">
-        <v>-0.272</v>
-      </c>
-      <c r="X147" s="22" t="n">
-        <v>-0.06900000000000001</v>
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>-12.075</v>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>-28.569</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="J147" s="12" t="n">
+        <v>-28.412</v>
+      </c>
+      <c r="L147" s="12" t="n">
+        <v>-332.686</v>
+      </c>
+      <c r="N147" s="12" t="n">
+        <v>-403.648</v>
+      </c>
+      <c r="T147" s="12" t="n">
+        <v>-14.061</v>
+      </c>
+      <c r="U147" s="12" t="n">
+        <v>-5.638</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>-28.569</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>-28.412</v>
+      </c>
+      <c r="X147" s="12" t="n">
+        <v>-403.648</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 행사에 따른 주식 발행</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="n">
-        <v>172.017</v>
-      </c>
-      <c r="F148" s="22" t="n">
-        <v>196.955</v>
-      </c>
-      <c r="H148" s="22" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="J148" s="22" t="n">
-        <v>124.55</v>
-      </c>
-      <c r="L148" s="22" t="n">
-        <v>47.089</v>
-      </c>
-      <c r="N148" s="22" t="n">
-        <v>75.95099999999999</v>
+          <t>신주예약권 발행</t>
+        </is>
+      </c>
+      <c r="T148" s="22" t="n">
+        <v>3.958</v>
       </c>
       <c r="U148" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="22" t="n">
-        <v>196.955</v>
-      </c>
-      <c r="W148" s="22" t="n">
-        <v>124.55</v>
-      </c>
-      <c r="X148" s="22" t="n">
-        <v>75.95099999999999</v>
-      </c>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D149" s="12" t="n">
-        <v>172.017</v>
-      </c>
-      <c r="F149" s="12" t="n">
-        <v>116.955</v>
-      </c>
-      <c r="H149" s="12" t="n">
-        <v>23.448</v>
-      </c>
-      <c r="J149" s="12" t="n">
-        <v>124.278</v>
-      </c>
-      <c r="L149" s="12" t="n">
-        <v>47.089</v>
-      </c>
-      <c r="N149" s="12" t="n">
-        <v>75.88200000000001</v>
-      </c>
-      <c r="T149" s="12" t="n">
-        <v>3.958</v>
-      </c>
-      <c r="U149" s="12" t="n">
-        <v>1241.104</v>
-      </c>
-      <c r="V149" s="12" t="n">
-        <v>116.955</v>
-      </c>
-      <c r="W149" s="12" t="n">
-        <v>124.278</v>
-      </c>
-      <c r="X149" s="12" t="n">
-        <v>75.88200000000001</v>
+      <c r="A149" s="20" t="inlineStr">
+        <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="F149" s="22" t="n">
+        <v>-80</v>
+      </c>
+      <c r="J149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="22" t="n">
+        <v>-80</v>
+      </c>
+      <c r="W149" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="F150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" s="22" t="n">
+        <v>1241.104</v>
+      </c>
+      <c r="V150" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
+          <t>단기차입</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="22" t="n">
+        <v>150</v>
+      </c>
+      <c r="N151" s="22" t="n">
+        <v>150</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 상환</t>
+        </is>
+      </c>
+      <c r="H152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="22" t="n">
+        <v>-150</v>
+      </c>
+      <c r="N152" s="22" t="n">
+        <v>-150</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="22" t="n">
+        <v>-0.149</v>
+      </c>
+      <c r="J153" s="22" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="L153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="22" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
+        <is>
+          <t>신주예약권 행사에 따른 주식 발행</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>172.017</v>
+      </c>
+      <c r="F154" s="22" t="n">
+        <v>196.955</v>
+      </c>
+      <c r="H154" s="22" t="n">
+        <v>23.598</v>
+      </c>
+      <c r="J154" s="22" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="L154" s="22" t="n">
+        <v>47.089</v>
+      </c>
+      <c r="N154" s="22" t="n">
+        <v>75.95099999999999</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>196.955</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>75.95099999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="n">
+        <v>172.017</v>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>116.955</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>23.448</v>
+      </c>
+      <c r="J155" s="12" t="n">
+        <v>124.278</v>
+      </c>
+      <c r="L155" s="12" t="n">
+        <v>47.089</v>
+      </c>
+      <c r="N155" s="12" t="n">
+        <v>75.88200000000001</v>
+      </c>
+      <c r="T155" s="12" t="n">
+        <v>3.958</v>
+      </c>
+      <c r="U155" s="12" t="n">
+        <v>1241.104</v>
+      </c>
+      <c r="V155" s="12" t="n">
+        <v>116.955</v>
+      </c>
+      <c r="W155" s="12" t="n">
+        <v>124.278</v>
+      </c>
+      <c r="X155" s="12" t="n">
+        <v>75.88200000000001</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="D150" s="22" t="n">
+      <c r="D156" s="22" t="n">
         <v>-10.731</v>
       </c>
-      <c r="F150" s="22" t="n">
+      <c r="F156" s="22" t="n">
         <v>-671.624</v>
       </c>
-      <c r="H150" s="22" t="n">
+      <c r="H156" s="22" t="n">
         <v>781.72</v>
       </c>
-      <c r="J150" s="22" t="n">
+      <c r="J156" s="22" t="n">
         <v>1717.107</v>
       </c>
-      <c r="L150" s="22" t="n">
+      <c r="L156" s="22" t="n">
         <v>-336.902</v>
       </c>
-      <c r="N150" s="22" t="n">
+      <c r="N156" s="22" t="n">
         <v>-162.559</v>
       </c>
-      <c r="T150" s="22" t="n">
+      <c r="T156" s="22" t="n">
         <v>-263.597</v>
       </c>
-      <c r="U150" s="22" t="n">
+      <c r="U156" s="22" t="n">
         <v>1695.998</v>
       </c>
-      <c r="V150" s="22" t="n">
+      <c r="V156" s="22" t="n">
         <v>-671.624</v>
       </c>
-      <c r="W150" s="22" t="n">
+      <c r="W156" s="22" t="n">
         <v>1717.107</v>
       </c>
-      <c r="X150" s="22" t="n">
+      <c r="X156" s="22" t="n">
         <v>-162.559</v>
       </c>
     </row>
@@ -8353,7 +8732,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -9703,7 +10082,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -9755,7 +10134,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -9807,7 +10186,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -9859,7 +10238,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -9911,7 +10290,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -9963,7 +10342,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10015,7 +10394,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10025,43 +10404,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10085,7 +10464,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10137,7 +10516,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10189,7 +10568,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10241,7 +10620,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10293,7 +10672,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10345,7 +10724,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10415,7 +10794,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -10467,7 +10846,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -10477,49 +10856,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -10529,49 +10908,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -10581,49 +10960,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -10633,43 +11012,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -10693,7 +11072,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -10745,7 +11124,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -10797,7 +11176,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -10849,7 +11228,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -12677,421 +13056,421 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>ABEJA 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>가이던스 history fy26 영업이익</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>25.10 최초</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>26.4 상향</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>26.7 상향</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>7.1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>실적</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>7.1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
         <is>
           <t>가이던스 history fy26 매출</t>
         </is>
       </c>
-      <c r="B11" s="53" t="n"/>
-      <c r="C11" s="53" t="n"/>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="54" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>25.10 최초</t>
         </is>
       </c>
-      <c r="B13" s="56" t="n">
+      <c r="B13" s="57" t="n">
         <v>44</v>
       </c>
-      <c r="C13" s="57" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>26.4</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="57" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>26.7</t>
         </is>
       </c>
-      <c r="B15" s="56" t="n">
+      <c r="B15" s="57" t="n">
         <v>45.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>실적</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="57" t="n">
         <v>45.77</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>컨센서스</t>
         </is>
       </c>
-      <c r="B18" s="53" t="n"/>
-      <c r="C18" s="53" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="inlineStr">
+      <c r="A19" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B19" s="54" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C19" s="54" t="inlineStr">
+      <c r="C19" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>FY8/27 매출</t>
         </is>
       </c>
-      <c r="B20" s="56" t="n">
+      <c r="B20" s="57" t="n">
         <v>54.1</v>
       </c>
-      <c r="C20" s="57" t="inlineStr">
+      <c r="C20" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>애널리스트</t>
         </is>
       </c>
-      <c r="B21" s="58" t="n">
+      <c r="B21" s="59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>4Q 증감 요인 vs 3Q</t>
         </is>
       </c>
-      <c r="B23" s="53" t="n"/>
-      <c r="C23" s="53" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C24" s="54" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>3Q 영업이익</t>
         </is>
       </c>
-      <c r="B25" s="56" t="n">
+      <c r="B25" s="57" t="n">
         <v>1.82</v>
       </c>
-      <c r="C25" s="57" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>증수</t>
         </is>
       </c>
-      <c r="B26" s="56" t="n">
+      <c r="B26" s="57" t="n">
         <v>1.9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>원가</t>
         </is>
       </c>
-      <c r="B27" s="56" t="n">
+      <c r="B27" s="57" t="n">
         <v>-0.85</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>인건비</t>
         </is>
       </c>
-      <c r="B28" s="56" t="n">
+      <c r="B28" s="57" t="n">
         <v>-0.32</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>채용교육비</t>
         </is>
       </c>
-      <c r="B29" s="56" t="n">
+      <c r="B29" s="57" t="n">
         <v>-0.41</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="56" t="inlineStr">
         <is>
           <t>업무위탁</t>
         </is>
       </c>
-      <c r="B30" s="56" t="n">
+      <c r="B30" s="57" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="B31" s="56" t="n">
+      <c r="B31" s="57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>기타(연구용 로봇 등)</t>
         </is>
       </c>
-      <c r="B32" s="56" t="n">
+      <c r="B32" s="57" t="n">
         <v>-0.61</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="55" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>4Q 영업이익</t>
         </is>
       </c>
-      <c r="B33" s="56" t="n">
+      <c r="B33" s="57" t="n">
         <v>1.43</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="54" t="inlineStr">
         <is>
           <t>FY 증감 요인</t>
         </is>
       </c>
-      <c r="B35" s="53" t="n"/>
-      <c r="C35" s="53" t="n"/>
+      <c r="B35" s="54" t="n"/>
+      <c r="C35" s="54" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="B36" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C36" s="54" t="inlineStr">
+      <c r="C36" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="55" t="inlineStr">
+      <c r="A37" s="56" t="inlineStr">
         <is>
           <t>FY25 영업이익</t>
         </is>
       </c>
-      <c r="B37" s="56" t="n">
+      <c r="B37" s="57" t="n">
         <v>4.45</v>
       </c>
-      <c r="C37" s="57" t="inlineStr">
+      <c r="C37" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>증수</t>
         </is>
       </c>
-      <c r="B38" s="56" t="n">
+      <c r="B38" s="57" t="n">
         <v>9.92</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>원가</t>
         </is>
       </c>
-      <c r="B39" s="56" t="n">
+      <c r="B39" s="57" t="n">
         <v>-4.36</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>매출총이익까지</t>
         </is>
       </c>
-      <c r="B40" s="56" t="n">
+      <c r="B40" s="57" t="n">
         <v>5.56</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
       </c>
-      <c r="B41" s="56" t="n">
+      <c r="B41" s="57" t="n">
         <v>-2.91</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n">
+      <c r="B42" s="57" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -13115,24 +13494,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
